--- a/inventory/files/2026-W40/STA_EU_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_EU_AUTO_2026-W40.xlsx
@@ -1539,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="14" min="1" max="1"/>
@@ -1690,81 +1690,41 @@
     <row r="9" customFormat="1" s="17">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AH-HLKITA</t>
+          <t>AH-RCTIRE10A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3307</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-RCTIRE10A</t>
+          <t>AH-TRKITA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2160</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AH-TRKITA</t>
+          <t>AH-RCINT14A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1385</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-RCPAINTA</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AH-RCINT14A</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AH-RCPL-B14A</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AH-GLASSCOATA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AH-RCWHL14A</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/inventory/files/2026-W40/STA_EU_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_EU_AUTO_2026-W40.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2372</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="10">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1517</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="11">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
